--- a/datf_core/test/testcases/testcase_template.xlsx
+++ b/datf_core/test/testcases/testcase_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\suresh\poc\project\s2ttestingtool\test\testcases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My_Workspaces\GitHub\DATF_Other\Editions\QE_ATF\datf_core\test\testcases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DF6521-B2DE-45B2-A6EA-14A18AACBDF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048F311E-FCE4-4390-A07C-FC6815C83751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="testcase" sheetId="1" r:id="rId1"/>
@@ -765,12 +765,9 @@
       <c r="B41" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7 B20" xr:uid="{5C998984-B12B-4920-B7BE-2FCA4650DBA8}">
       <formula1>"avro,json,parquet,delimitedfile,delta,table"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6 B19" xr:uid="{9FF30855-8436-42A8-9825-752EC287DC20}">
-      <formula1>"aws-s3,redshift,oracle"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27 B14 B3" xr:uid="{01C4EF0D-7247-4C84-B339-7110C6C1DDBE}">
       <formula1>"Auto,Manual"</formula1>
@@ -778,6 +775,12 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10 B23" xr:uid="{287F7A43-6C4E-4AC8-8370-E84529DD0FCD}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{39B9CD63-7924-43A4-B5BA-B5D491D3247A}">
+      <formula1>"s2tcompare,likeobjectcompare"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6 B19" xr:uid="{28E17073-2E2C-4D6A-90EE-6A59D35E5C2D}">
+      <formula1>"aws-s3,redshift,oracle,mysql,postgres,sqlserver,bigquery,snowflake,databricks"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/datf_core/test/testcases/testcase_template.xlsx
+++ b/datf_core/test/testcases/testcase_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My_Workspaces\GitHub\DATF_Other\Editions\QE_ATF\datf_core\test\testcases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048F311E-FCE4-4390-A07C-FC6815C83751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3A6DFC-05A8-4094-A0C0-2E6FEE125A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
